--- a/data/trans_orig/IP25A01_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25A01_2023-Provincia-trans_orig.xlsx
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>17675</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35304</t>
+          <t>36271</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52574</t>
+          <t>52226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36754</t>
+          <t>36871</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52971</t>
+          <t>52600</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76925</t>
+          <t>77096</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100551</t>
+          <t>100813</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,04%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>25560</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30320</t>
+          <t>30564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51554</t>
+          <t>51103</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>16517</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28726</t>
+          <t>29591</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>28490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>24812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51741</t>
+          <t>52073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21974</t>
+          <t>19974</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60077</t>
+          <t>60229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38955</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62195</t>
+          <t>62718</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62985</t>
+          <t>61730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114243</t>
+          <t>113007</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34444</t>
+          <t>34613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89479</t>
+          <t>95636</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>41199</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66562</t>
+          <t>66620</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85541</t>
+          <t>87766</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>158044</t>
+          <t>156457</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31433</t>
+          <t>30743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19023</t>
+          <t>18676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32123</t>
+          <t>31468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40743</t>
+          <t>41734</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57903</t>
+          <t>59226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>47,59%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>21704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33046</t>
+          <t>33307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>31169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44407</t>
+          <t>44332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57524</t>
+          <t>57059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73976</t>
+          <t>74625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>10927</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23286</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26418</t>
+          <t>26984</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>13627</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34187</t>
+          <t>33569</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30570</t>
+          <t>30707</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>56811</t>
+          <t>55872</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32690</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46969</t>
+          <t>46680</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31687</t>
+          <t>31731</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56440</t>
+          <t>57439</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69304</t>
+          <t>67981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98533</t>
+          <t>97627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,41%</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>847</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>955</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>10910</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12400</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>22038</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>21989</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35543</t>
+          <t>34717</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,15%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>17711</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>25946</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>34425</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>47948</t>
+          <t>48564</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,55%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19765</t>
+          <t>19709</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>25617</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>20603</t>
+          <t>20511</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>33085</t>
+          <t>32812</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>38576</t>
+          <t>38353</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>54214</t>
+          <t>54757</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20804</t>
+          <t>20873</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16048</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28818</t>
+          <t>28270</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>30988</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>45411</t>
+          <t>46246</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22654</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>28980</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8635</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36477</t>
+          <t>36432</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>30738</t>
+          <t>30676</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>49154</t>
+          <t>48230</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>54080</t>
+          <t>53401</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>79645</t>
+          <t>79023</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>89255</t>
+          <t>90489</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>119540</t>
+          <t>121898</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>48000</t>
+          <t>47462</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>66859</t>
+          <t>67287</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>56167</t>
+          <t>56052</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>84168</t>
+          <t>84423</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>110268</t>
+          <t>111417</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>144662</t>
+          <t>145312</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>385</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>10398</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14192</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>69550</t>
+          <t>70130</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>88819</t>
+          <t>88867</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>87954</t>
+          <t>88205</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>109425</t>
+          <t>109646</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>164030</t>
+          <t>165783</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>192411</t>
+          <t>193494</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>40395</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>58420</t>
+          <t>58354</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>40343</t>
+          <t>40387</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>60539</t>
+          <t>60391</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>85612</t>
+          <t>83889</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>113223</t>
+          <t>111863</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>39600</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>27604</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>31357</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>57021</t>
+          <t>55948</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>46803</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>77160</t>
+          <t>76225</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>59949</t>
+          <t>59199</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>90821</t>
+          <t>89540</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>114060</t>
+          <t>112334</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>158085</t>
+          <t>153959</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>243867</t>
+          <t>246619</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>309369</t>
+          <t>311198</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>322697</t>
+          <t>325464</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>378834</t>
+          <t>381180</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>588757</t>
+          <t>588608</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>677391</t>
+          <t>675183</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>259330</t>
+          <t>258461</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>339537</t>
+          <t>338714</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>290080</t>
+          <t>288335</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>347904</t>
+          <t>345296</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>563647</t>
+          <t>567161</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>664596</t>
+          <t>661852</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A01_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25A01_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10477</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6060</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16144</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10029</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5419</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17675</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37874</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31811</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>43951</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>59,04%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>49,59%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>68,52%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>44268</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>36271</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>52226</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>60,41%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>49,5%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>71,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>31764</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>26586</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52600</t>
+          <t>38332</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>89348</t>
+          <t>69638</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77096</t>
+          <t>60387</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100813</t>
+          <t>78161</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15794</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10892</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21865</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>24,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18985</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12229</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25560</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>25,91%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>16754</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30564</t>
+          <t>22103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>40799</t>
+          <t>32549</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30402</t>
+          <t>25283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>40690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2967</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7815</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6370</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1724</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>11974</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>12492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>8919</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16517</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18533</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11816</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26053</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18229</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8659</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29591</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28490</t>
+          <t>23186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>34459</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52073</t>
+          <t>44342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>46102</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35191</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>55494</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>44595</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19974</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>60229</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>35,49%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51016</t>
+          <t>44395</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40100</t>
+          <t>35454</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62718</t>
+          <t>52832</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>95611</t>
+          <t>90497</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61730</t>
+          <t>76681</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113007</t>
+          <t>104571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>48234</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>38314</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>61472</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>41,64%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>33,08%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>53,07%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>56455</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>34613</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>95636</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>44,93%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>27,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53363</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41199</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66620</t>
+          <t>41902</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>109818</t>
+          <t>81295</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87766</t>
+          <t>67010</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>156457</t>
+          <t>96101</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>215169</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>215169</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>215169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4232</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2459</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5949</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1976,102 +1976,102 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2262</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5472</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>4731</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2248</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>9420</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
           <t>4,11%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>2717</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>6148</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>5070</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>2134</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>9418</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>21857</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16359</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27633</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,81%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>46,54%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>25080</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18896</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>30743</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,79%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,99%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>19018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31468</t>
+          <t>30811</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>49725</t>
+          <t>46797</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41734</t>
+          <t>39008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59226</t>
+          <t>55582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33746</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>27277</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>39500</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>56,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>45,94%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>66,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>27387</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>21704</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33307</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>58,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38199</t>
+          <t>26037</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31169</t>
+          <t>20565</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44332</t>
+          <t>32051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>65586</t>
+          <t>59783</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57059</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74625</t>
+          <t>67560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>57278</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>57278</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>57278</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>124441</t>
+          <t>114982</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124441</t>
+          <t>114982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124441</t>
+          <t>114982</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,107 +2427,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4458</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1181</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10695</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4823</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11656</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>14,92%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10927</t>
+          <t>12207</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7015</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2981</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14973</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>20,75%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>7259</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3677</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12602</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>22673</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>21632</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>12731</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>31687</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>29,98%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>17,64%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>43,91%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>19824</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>13202</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>26984</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>29,73%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>19,8%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>40,47%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23482</t>
+          <t>19843</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33569</t>
+          <t>27058</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>43306</t>
+          <t>41475</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30707</t>
+          <t>29811</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>55872</t>
+          <t>54679</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>39056</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>29161</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>50725</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,12%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>40,41%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>70,29%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>39602</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>32718</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>46680</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>59,39%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>70,0%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42674</t>
+          <t>40535</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>33410</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57439</t>
+          <t>48094</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>82275</t>
+          <t>79591</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67981</t>
+          <t>65895</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97627</t>
+          <t>93286</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>66684</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>66684</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>66684</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>67592</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>67592</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>67592</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>144818</t>
+          <t>139754</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>144818</t>
+          <t>139754</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>144818</t>
+          <t>139754</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,107 +2996,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>847</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4377</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1672</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10364</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>11,06%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>26,19%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2524</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>4376</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>9399</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10910</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>15178</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10817</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>19965</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>38,35%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>27,33%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>50,44%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>11596</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>8075</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>16013</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>33,6%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>23,4%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>46,4%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>28166</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21989</t>
+          <t>21600</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34717</t>
+          <t>33674</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>44,79%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>19753</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>15032</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>24524</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>49,91%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>37,98%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>61,96%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>22345</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>17711</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>25946</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>64,74%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>51,32%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>75,18%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>22944</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24416</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>41956</t>
+          <t>42697</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>35456</t>
+          <t>36552</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>48564</t>
+          <t>49261</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,52%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,72 +3565,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>3369</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>7578</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -3678,72 +3678,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>5870</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>10241</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>11,99%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>20,92%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>6868</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>3626</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>11422</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -3791,72 +3791,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>23393</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>17964</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>29201</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>59,66%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>20066</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>15156</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>25617</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>43,46%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>32,83%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>55,49%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>20476</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>32812</t>
+          <t>25652</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>46482</t>
+          <t>43869</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>38353</t>
+          <t>36541</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>54757</t>
+          <t>51138</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -3904,72 +3904,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>19100</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>13796</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>24192</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>39,03%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>28,19%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>49,43%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>15863</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>11397</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>20873</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>34,36%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>24,69%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>45,21%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>22450</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28270</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>38313</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>30988</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>46246</t>
+          <t>41077</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -4017,57 +4017,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4134,72 +4134,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>5547</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>11297</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>8,06%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>11675</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>6301</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>22818</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11108</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>11108</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30111</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>12842</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19053</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21968</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>26803</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36432</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -4360,72 +4360,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>61015</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>50145</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>72080</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>35,75%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>51,39%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>39177</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>30676</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>48230</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>32,24%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>25,24%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>39,69%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>66156</t>
+          <t>39824</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>53401</t>
+          <t>31088</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>79023</t>
+          <t>49742</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>105333</t>
+          <t>100839</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>90489</t>
+          <t>87672</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>121898</t>
+          <t>115574</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,49%</t>
         </is>
       </c>
     </row>
@@ -4473,72 +4473,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>60010</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>71694</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>42,79%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>35,61%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>51,12%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>57821</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>47462</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>67287</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>39,06%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>55,37%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>69109</t>
+          <t>56708</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>56052</t>
+          <t>48026</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>84423</t>
+          <t>65962</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>126930</t>
+          <t>116718</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>111417</t>
+          <t>103618</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>145312</t>
+          <t>131606</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -4586,57 +4586,57 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>140249</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>140249</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>140249</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>121515</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>121515</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>121515</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>119514</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>119514</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>119514</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>276169</t>
+          <t>259763</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>276169</t>
+          <t>259763</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>276169</t>
+          <t>259763</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4703,72 +4703,72 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>5636</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>2611</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>1746</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>1616</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>7302</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>349</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -4816,72 +4816,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>5910</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2754</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>11227</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>2601</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>743</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>7342</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>813</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14464</t>
+          <t>15811</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -4929,72 +4929,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>102824</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>91490</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>113116</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>64,62%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>57,5%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>71,09%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>79518</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>70130</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>88867</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>60,69%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>53,53%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>67,83%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>99301</t>
+          <t>86040</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>88205</t>
+          <t>74621</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>109646</t>
+          <t>96383</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>178819</t>
+          <t>188864</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>165783</t>
+          <t>174725</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>193494</t>
+          <t>203946</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>68,19%</t>
         </is>
       </c>
     </row>
@@ -5042,72 +5042,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>48814</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>38319</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>59187</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>30,68%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>24,08%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>37,2%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>48511</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>39102</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>58354</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>37,03%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>29,85%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>44,54%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>49810</t>
+          <t>50670</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>40387</t>
+          <t>40669</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>60391</t>
+          <t>61859</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>98321</t>
+          <t>99484</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>83889</t>
+          <t>84755</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>111863</t>
+          <t>113085</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -5155,57 +5155,57 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>131016</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>131016</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>131016</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139973</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139973</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139973</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>287453</t>
+          <t>299090</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>287453</t>
+          <t>299090</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>287453</t>
+          <t>299090</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5272,72 +5272,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>16697</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>10396</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>25550</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>24259</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>16804</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>35969</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>26781</t>
+          <t>29533</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>41773</t>
+          <t>38054</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>28143</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>55948</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -5385,72 +5385,72 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>68328</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>55354</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>83056</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>60753</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>46803</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>76225</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>11,62%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>73045</t>
+          <t>57564</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>59199</t>
+          <t>46596</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>89540</t>
+          <t>72067</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>133798</t>
+          <t>125892</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>112334</t>
+          <t>110261</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>153959</t>
+          <t>145889</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -5498,72 +5498,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>329874</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>302197</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>353176</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>47,16%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>43,21%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>50,5%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>406</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>284123</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>246619</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>311198</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>43,3%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>37,59%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>47,43%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>352667</t>
+          <t>279373</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>325464</t>
+          <t>257937</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>381180</t>
+          <t>300503</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>636791</t>
+          <t>609247</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>588608</t>
+          <t>578410</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>675183</t>
+          <t>642191</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>286968</t>
+          <t>284509</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>258461</t>
+          <t>258578</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>338714</t>
+          <t>312152</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>317028</t>
+          <t>261577</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>288335</t>
+          <t>242563</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>345296</t>
+          <t>282224</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>603997</t>
+          <t>546085</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>567161</t>
+          <t>514903</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>661852</t>
+          <t>578598</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -5724,57 +5724,57 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>699407</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>656104</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>656104</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>656104</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619872</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619872</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>760255</t>
+          <t>619872</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1416359</t>
+          <t>1319278</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1416359</t>
+          <t>1319278</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1416359</t>
+          <t>1319278</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
